--- a/在校学生数统计.xlsx
+++ b/在校学生数统计.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5be2da34601d9e64/文档/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="601" documentId="8_{DF5A585F-D9A0-4585-8435-8FE8BF72D900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F01731-5BEA-4861-9D1C-8DA606E89C85}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{16D59AF9-2171-4202-A97E-C9423700A2C8}"/>
+    <workbookView windowWidth="24000" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="表 3" sheetId="2" r:id="rId1"/>
@@ -21,9 +15,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,15 +31,18 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{8B8157FE-44FC-4FC5-9A71-D57EF4CE040C}" keepAlive="1" name="查询 - 表 3" description="与工作簿中“表 3”查询的连接。" type="5" refreshedVersion="0" background="1" saveData="1">
-    <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=&quot;表 3&quot;;Extended Properties=&quot;&quot;" command="SELECT * FROM [表 3]"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="查询 - 表 3" description="与工作簿中“表 3”查询的连接。" type="5" background="1" refreshedVersion="2" saveData="1">
+    <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=&quot;表 3&quot;;Extended Properties=&quot;&quot;" command="SELECT * FROM [表 3]" commandType="2"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+  <si>
+    <t>高等教育</t>
+  </si>
   <si>
     <t>普通高中教育学生数</t>
   </si>
@@ -62,88 +56,121 @@
     <t>小学教育学生数</t>
   </si>
   <si>
+    <t>高中教育</t>
+  </si>
+  <si>
+    <t>义务教育</t>
+  </si>
+  <si>
+    <t>小学招生人数</t>
+  </si>
+  <si>
+    <t>初中招生人数</t>
+  </si>
+  <si>
+    <t>中专招生人数</t>
+  </si>
+  <si>
+    <t>普高招生人数</t>
+  </si>
+  <si>
+    <t>高等教育招生人数</t>
+  </si>
+  <si>
+    <t>义务教育招生数</t>
+  </si>
+  <si>
+    <t>高中教育招生数</t>
+  </si>
+  <si>
+    <t>高等教育招生比</t>
+  </si>
+  <si>
+    <t>义务教育招生比</t>
+  </si>
+  <si>
+    <t>高中教育招生比</t>
+  </si>
+  <si>
+    <t>总人口数（万）</t>
+  </si>
+  <si>
+    <t>城镇人口/总人口</t>
+  </si>
+  <si>
+    <t>小学生师比</t>
+  </si>
+  <si>
+    <t>初中生师比</t>
+  </si>
+  <si>
+    <t>17.12:1</t>
+  </si>
+  <si>
+    <t>12.41:1</t>
+  </si>
+  <si>
+    <t>16.98:1</t>
+  </si>
+  <si>
+    <t>12.52:1</t>
+  </si>
+  <si>
+    <t>16.97:1</t>
+  </si>
+  <si>
+    <t>12.79:1</t>
+  </si>
+  <si>
+    <t>16.85:1</t>
+  </si>
+  <si>
+    <t>12.88:1</t>
+  </si>
+  <si>
+    <t>16.67:1</t>
+  </si>
+  <si>
+    <t>12.73:1</t>
+  </si>
+  <si>
+    <t>16.33:1</t>
+  </si>
+  <si>
+    <t>12.64:1</t>
+  </si>
+  <si>
+    <t>16.19:1</t>
+  </si>
+  <si>
+    <t>12.72:1</t>
+  </si>
+  <si>
     <t xml:space="preserve">590957	</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等教育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高中教育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>义务教育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.28:1</t>
+  </si>
+  <si>
+    <t>12.84:1</t>
+  </si>
+  <si>
+    <t>预测2024</t>
+  </si>
+  <si>
+    <t>预测2025</t>
+  </si>
+  <si>
+    <t>预测2026</t>
   </si>
   <si>
     <t>恩格尔系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小学招生人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初中招生人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中专招生人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普高招生人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等教育招生人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>义务教育招生数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高中教育招生数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>出生人数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等教育招生比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>义务教育招生比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高中教育招生比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预测2024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预测2025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>预测2026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总人口数（万）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>城镇人口/总人口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年份</t>
   </si>
   <si>
     <t>义务教育阶段生均</t>
@@ -158,6 +185,24 @@
     <t>总</t>
   </si>
   <si>
+    <t>义务教育总</t>
+  </si>
+  <si>
+    <t>高中教育总</t>
+  </si>
+  <si>
+    <t>高等教育总</t>
+  </si>
+  <si>
+    <t>总()</t>
+  </si>
+  <si>
+    <t>义务教育生师比</t>
+  </si>
+  <si>
+    <t>本科就业率</t>
+  </si>
+  <si>
     <t>2016 年</t>
   </si>
   <si>
@@ -173,6 +218,18 @@
     <t>495.92亿</t>
   </si>
   <si>
+    <t>267.4522亿</t>
+  </si>
+  <si>
+    <t>91.5254亿</t>
+  </si>
+  <si>
+    <t>112.5077亿</t>
+  </si>
+  <si>
+    <t>471.4853亿</t>
+  </si>
+  <si>
     <t>2017 年</t>
   </si>
   <si>
@@ -188,6 +245,18 @@
     <t>503.80亿</t>
   </si>
   <si>
+    <t>279.8679亿</t>
+  </si>
+  <si>
+    <t>97.4366亿</t>
+  </si>
+  <si>
+    <t>115.7238亿</t>
+  </si>
+  <si>
+    <t>493.0282亿</t>
+  </si>
+  <si>
     <t>2018 年</t>
   </si>
   <si>
@@ -203,6 +272,18 @@
     <t>508.60亿</t>
   </si>
   <si>
+    <t>271.8626亿</t>
+  </si>
+  <si>
+    <t>92.5165亿</t>
+  </si>
+  <si>
+    <t>120.6006亿</t>
+  </si>
+  <si>
+    <t>484.9797亿</t>
+  </si>
+  <si>
     <t>2019 年</t>
   </si>
   <si>
@@ -218,6 +299,18 @@
     <t>497.16亿</t>
   </si>
   <si>
+    <t>269.5978亿</t>
+  </si>
+  <si>
+    <t>94.8163亿</t>
+  </si>
+  <si>
+    <t>127.4309亿</t>
+  </si>
+  <si>
+    <t>491.8450亿</t>
+  </si>
+  <si>
     <t>2020 年</t>
   </si>
   <si>
@@ -233,6 +326,18 @@
     <t>522.58亿</t>
   </si>
   <si>
+    <t>289.6829亿</t>
+  </si>
+  <si>
+    <t>103.3552亿</t>
+  </si>
+  <si>
+    <t>114.9781亿</t>
+  </si>
+  <si>
+    <t>508.0162亿</t>
+  </si>
+  <si>
     <t>2021 年</t>
   </si>
   <si>
@@ -248,6 +353,18 @@
     <t>483.95亿</t>
   </si>
   <si>
+    <t>286.3879亿</t>
+  </si>
+  <si>
+    <t>104.5238亿</t>
+  </si>
+  <si>
+    <t>122.4476亿</t>
+  </si>
+  <si>
+    <t>513.3593亿</t>
+  </si>
+  <si>
     <t>2022 年</t>
   </si>
   <si>
@@ -263,6 +380,18 @@
     <t>503.83亿</t>
   </si>
   <si>
+    <t>270.2604亿</t>
+  </si>
+  <si>
+    <t>103.4368亿</t>
+  </si>
+  <si>
+    <t>120.7671亿</t>
+  </si>
+  <si>
+    <t>494.4644亿</t>
+  </si>
+  <si>
     <t>2023 年</t>
   </si>
   <si>
@@ -278,82 +407,6 @@
     <t>527.90亿</t>
   </si>
   <si>
-    <t>义务教育总</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高中教育总</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等教育总</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年份</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>91.5254亿</t>
-  </si>
-  <si>
-    <t>279.8679亿</t>
-  </si>
-  <si>
-    <t>97.4366亿</t>
-  </si>
-  <si>
-    <t>115.7238亿</t>
-  </si>
-  <si>
-    <t>271.8626亿</t>
-  </si>
-  <si>
-    <t>92.5165亿</t>
-  </si>
-  <si>
-    <t>120.6006亿</t>
-  </si>
-  <si>
-    <t>267.4522亿</t>
-  </si>
-  <si>
-    <t>269.5978亿</t>
-  </si>
-  <si>
-    <t>94.8163亿</t>
-  </si>
-  <si>
-    <t>127.4309亿</t>
-  </si>
-  <si>
-    <t>289.6829亿</t>
-  </si>
-  <si>
-    <t>103.3552亿</t>
-  </si>
-  <si>
-    <t>114.9781亿</t>
-  </si>
-  <si>
-    <t>286.3879亿</t>
-  </si>
-  <si>
-    <t>104.5238亿</t>
-  </si>
-  <si>
-    <t>122.4476亿</t>
-  </si>
-  <si>
-    <t>270.2604亿</t>
-  </si>
-  <si>
-    <t>103.4368亿</t>
-  </si>
-  <si>
-    <t>120.7671亿</t>
-  </si>
-  <si>
     <t>282.4349亿</t>
   </si>
   <si>
@@ -363,127 +416,33 @@
     <t>125.1818亿</t>
   </si>
   <si>
-    <t>471.4853亿</t>
-  </si>
-  <si>
-    <t>493.0282亿</t>
-  </si>
-  <si>
-    <t>484.9797亿</t>
-  </si>
-  <si>
-    <t>总()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>491.8450亿</t>
-  </si>
-  <si>
-    <t>508.0162亿</t>
-  </si>
-  <si>
-    <t>513.3593亿</t>
-  </si>
-  <si>
-    <t>494.4644亿</t>
-  </si>
-  <si>
     <t>511.3354亿</t>
   </si>
   <si>
-    <t>112.5077亿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小学生师比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初中生师比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.28:1</t>
-  </si>
-  <si>
-    <t>12.84:1</t>
-  </si>
-  <si>
-    <t>16.19:1</t>
-  </si>
-  <si>
-    <t>12.72:1</t>
-  </si>
-  <si>
-    <t>16.33:1</t>
-  </si>
-  <si>
-    <t>12.64:1</t>
-  </si>
-  <si>
-    <t>16.67:1</t>
-  </si>
-  <si>
-    <t>12.73:1</t>
-  </si>
-  <si>
-    <t>16.85:1</t>
-  </si>
-  <si>
-    <t>12.88:1</t>
-  </si>
-  <si>
-    <t>16.97:1</t>
-  </si>
-  <si>
-    <t>12.79:1</t>
-  </si>
-  <si>
-    <t>16.98:1</t>
-  </si>
-  <si>
-    <t>12.52:1</t>
-  </si>
-  <si>
-    <t>17.12:1</t>
-  </si>
-  <si>
-    <t>12.41:1</t>
-  </si>
-  <si>
-    <t>义务教育生师比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>线性回归系数k</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>线性回归系数b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>相关系数r</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -492,70 +451,215 @@
       <sz val="8"/>
       <color rgb="FF4B4B4B"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4B4B4B"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF4B4B4B"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <color rgb="FF808080"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="宋体"/>
-      <family val="2"/>
+      <color rgb="FF4B4B4B"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF4B4B4B"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,8 +678,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -616,9 +906,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -626,26 +1158,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -653,47 +1194,78 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -739,7 +1311,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -772,26 +1344,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -824,23 +1379,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1002,116 +1540,111 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8EBC83-6FF3-4259-B99F-0AF5CF82110E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V47"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.53125" customWidth="1"/>
-    <col min="9" max="9" width="42.33203125" customWidth="1"/>
-    <col min="10" max="10" width="39.59765625" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.66371681415929" customWidth="1"/>
+    <col min="8" max="8" width="13.5309734513274" customWidth="1"/>
+    <col min="9" max="9" width="42.3362831858407" customWidth="1"/>
+    <col min="10" max="10" width="39.6017699115044" customWidth="1"/>
+    <col min="11" max="11" width="18.3362831858407" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="15" width="12.3984375" customWidth="1"/>
-    <col min="16" max="16" width="14.265625" customWidth="1"/>
-    <col min="17" max="17" width="11.19921875" customWidth="1"/>
-    <col min="21" max="21" width="16.73046875" customWidth="1"/>
-    <col min="22" max="22" width="13.53125" customWidth="1"/>
-    <col min="23" max="23" width="12.9296875" customWidth="1"/>
+    <col min="14" max="15" width="12.3982300884956" customWidth="1"/>
+    <col min="16" max="16" width="14.2654867256637" customWidth="1"/>
+    <col min="17" max="17" width="11.2035398230088" customWidth="1"/>
+    <col min="21" max="21" width="16.7345132743363" customWidth="1"/>
+    <col min="22" max="22" width="13.5309734513274" customWidth="1"/>
+    <col min="23" max="23" width="12.929203539823" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="33.75" x14ac:dyDescent="0.4">
+    <row r="1" ht="33.75" spans="2:22">
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>2013</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>599526</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>192672</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>192672</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>644993</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>1361868</v>
       </c>
       <c r="G2">
@@ -1122,19 +1655,19 @@
         <f t="shared" ref="H2:H11" si="1">SUM(E2:F2)</f>
         <v>2006861</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>217645</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="2">
         <v>218370</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>61055</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="2">
         <v>151131</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>166248</v>
       </c>
       <c r="N2">
@@ -1145,33 +1678,33 @@
         <f>SUM(K2:L2)</f>
         <v>212186</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="2">
         <v>0.49</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="2">
         <v>2668.1</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="2">
         <v>55.7</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+    <row r="3" ht="15" spans="1:20">
       <c r="A3">
         <v>2014</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="2">
         <v>618273</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>415736</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="3">
         <v>150044</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <v>622883</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <v>1268804</v>
       </c>
       <c r="G3">
@@ -1182,19 +1715,19 @@
         <f t="shared" si="1"/>
         <v>1891687</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="2">
         <v>190001</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="2">
         <v>209897</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="3">
         <v>43508</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="3">
         <v>132338</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="2">
         <v>168940</v>
       </c>
       <c r="N3">
@@ -1208,30 +1741,30 @@
       <c r="P3">
         <v>0.51</v>
       </c>
-      <c r="S3" s="12">
+      <c r="S3" s="16">
         <v>2641.9</v>
       </c>
-      <c r="T3" s="12">
+      <c r="T3" s="16">
         <v>56.8</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2015</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="2">
         <v>632723</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>406263</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>134237</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <v>595518</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>1279766</v>
       </c>
       <c r="G4">
@@ -1242,19 +1775,19 @@
         <f t="shared" si="1"/>
         <v>1875284</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="2">
         <v>206046</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="2">
         <v>181172</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="2">
         <v>45498</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="2">
         <v>135162</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="2">
         <v>170014</v>
       </c>
       <c r="N4">
@@ -1265,33 +1798,33 @@
         <f>SUM(K4:L4)</f>
         <v>180660</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="2">
         <v>0.53</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="2">
         <v>2612.5</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4" s="2">
         <v>57.6</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+    <row r="5" ht="15" spans="1:22">
       <c r="A5">
         <v>2016</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="2">
         <v>642263</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
         <v>404209</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>129856</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <v>604277</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <v>1264211</v>
       </c>
       <c r="G5">
@@ -1302,19 +1835,19 @@
         <f t="shared" si="1"/>
         <v>1868488</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="2">
         <v>204937</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="2">
         <v>217027</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="2">
         <v>46958</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="2">
         <v>139534</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="2">
         <v>173218</v>
       </c>
       <c r="N5">
@@ -1325,39 +1858,39 @@
         <f>SUM(K5:L5)</f>
         <v>186492</v>
       </c>
-      <c r="P5" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="S5" s="5">
+      <c r="P5" s="2">
+        <v>0.55</v>
+      </c>
+      <c r="S5" s="2">
         <v>2567</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5" s="2">
         <v>58.8</v>
       </c>
-      <c r="U5" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="V5" s="16" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="V5" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:22">
       <c r="A6">
         <v>2017</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="2">
         <v>643872</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
         <v>413783</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>131774</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="2">
         <v>618704</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="2">
         <v>1228205</v>
       </c>
       <c r="G6">
@@ -1368,19 +1901,19 @@
         <f t="shared" si="1"/>
         <v>1846909</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="2">
         <v>189407</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="2">
         <v>221942</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="2">
         <v>44566</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="2">
         <v>141705</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="2">
         <v>171239</v>
       </c>
       <c r="N6">
@@ -1391,39 +1924,39 @@
         <f>SUM(K6:L6)</f>
         <v>186271</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="2">
         <v>0.6</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="2">
         <v>2526.1</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="2">
         <v>59.7</v>
       </c>
-      <c r="U6" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="V6" s="16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U6" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:22">
       <c r="A7">
         <v>2018</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="2">
         <v>658327</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="2">
         <v>408494</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>120897</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="2">
         <v>660635</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="2">
         <v>1201872</v>
       </c>
       <c r="G7">
@@ -1434,19 +1967,19 @@
         <f t="shared" si="1"/>
         <v>1862507</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="2">
         <v>201272</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="2">
         <v>224225</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="2">
         <v>35090</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="2">
         <v>129106</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="2">
         <v>175543</v>
       </c>
       <c r="N7">
@@ -1457,39 +1990,39 @@
         <f>SUM(K8:L8)</f>
         <v>193277</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="2">
         <v>0.64</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="2">
         <v>2484.4</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="2">
         <v>60.9</v>
       </c>
-      <c r="U7" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="V7" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="V7" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:22">
       <c r="A8">
         <v>2019</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="2">
         <v>700145</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="2">
         <v>418443</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>117863</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="2">
         <v>654524</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="2">
         <v>1185695</v>
       </c>
       <c r="G8">
@@ -1500,19 +2033,19 @@
         <f t="shared" si="1"/>
         <v>1840219</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="2">
         <v>196696</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="2">
         <v>210064</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="2">
         <v>43755</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="2">
         <v>149522</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="2">
         <v>203888</v>
       </c>
       <c r="N8">
@@ -1523,39 +2056,39 @@
         <f>SUM(K8:L8)</f>
         <v>193277</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8" s="2">
         <v>0.86</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="16">
         <v>2447.5</v>
       </c>
-      <c r="T8" s="5">
+      <c r="T8" s="2">
         <v>61.6</v>
       </c>
-      <c r="U8" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="V8" s="16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:22">
       <c r="A9">
         <v>2020</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>726957</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>428406</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>118915</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>622419</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>1187540</v>
       </c>
       <c r="G9">
@@ -1566,19 +2099,19 @@
         <f t="shared" si="1"/>
         <v>1809959</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>190858</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>188411</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="4">
         <v>44765</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>151566</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="4">
         <v>189064</v>
       </c>
       <c r="N9">
@@ -1589,39 +2122,39 @@
         <f>SUM(K9:L9)</f>
         <v>196331</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="2">
         <v>0.84</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="2">
         <v>2399.4</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="2">
         <v>62.6</v>
       </c>
-      <c r="U9" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="V9" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="V9" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:22">
       <c r="A10">
         <v>2021</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>755552</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="5">
         <v>450088</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="5">
         <v>131079</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="5">
         <v>601187</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="5">
         <v>1151039</v>
       </c>
       <c r="G10">
@@ -1632,16 +2165,16 @@
         <f t="shared" si="1"/>
         <v>1752226</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="5">
         <v>170160</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="5">
         <v>201841</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="5">
         <v>48777</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="5">
         <v>150919</v>
       </c>
       <c r="M10">
@@ -1655,36 +2188,36 @@
         <f>SUM(K10:L10)</f>
         <v>199696</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10" s="2">
         <v>2375.4</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="2">
         <v>63.4</v>
       </c>
-      <c r="U10" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="V10" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="V10" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:22">
       <c r="A11">
         <v>2022</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="5">
         <v>710245</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="5">
         <v>449767</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="6">
         <v>132660</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="5">
         <v>592175</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="5">
         <v>1111689</v>
       </c>
       <c r="G11">
@@ -1695,16 +2228,16 @@
         <f t="shared" si="1"/>
         <v>1703864</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="5">
         <v>164282</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="5">
         <v>201034</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="6">
         <v>45857</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="5">
         <v>148060</v>
       </c>
       <c r="M11">
@@ -1718,58 +2251,58 @@
         <f>SUM(K11:L11)</f>
         <v>193917</v>
       </c>
-      <c r="S11" s="12">
-        <v>2347.6999999999998</v>
-      </c>
-      <c r="T11" s="12">
+      <c r="S11" s="16">
+        <v>2347.7</v>
+      </c>
+      <c r="T11" s="16">
         <v>63.7</v>
       </c>
-      <c r="U11" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="V11" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="15" x14ac:dyDescent="0.4">
+      <c r="U11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="V11" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:22">
       <c r="A12">
         <v>2023</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="5">
         <v>715922</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="7">
         <v>436985</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="6">
         <v>123115</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="E12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="5">
         <v>1095277</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="7">
         <f t="shared" si="0"/>
         <v>560100</v>
       </c>
       <c r="H12">
         <v>1686234</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="5">
         <v>172337</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="5">
         <v>186575</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="6">
         <v>35641</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="5">
         <v>138568</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="6">
         <v>212078</v>
       </c>
       <c r="N12">
@@ -1780,41 +2313,41 @@
         <f>SUM(K12:L12)</f>
         <v>174209</v>
       </c>
-      <c r="S12" s="5">
+      <c r="S12" s="2">
         <v>2339.4</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T12" s="2">
         <v>64.7</v>
       </c>
-      <c r="U12" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="V12" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="U12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5">
         <v>724004</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="10">
+      <c r="C13" s="8"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="8">
         <v>572259.9</v>
       </c>
       <c r="H13">
         <v>1662384</v>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="3">
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6">
         <v>220883</v>
       </c>
       <c r="N13">
@@ -1825,28 +2358,28 @@
       </c>
       <c r="U13" s="17"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5">
         <v>726559.5</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="10">
-        <v>570889.69999999995</v>
+      <c r="C14" s="8"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="8">
+        <v>570889.7</v>
       </c>
       <c r="H14">
         <v>1629434</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="3">
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6">
         <v>226496</v>
       </c>
       <c r="N14">
@@ -1856,28 +2389,28 @@
         <v>188045</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5">
         <v>749094.9</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="10">
-        <v>540504.19999999995</v>
+      <c r="C15" s="8"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="8">
+        <v>540504.2</v>
       </c>
       <c r="H15">
         <v>1602655</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="3">
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="6">
         <v>232109</v>
       </c>
       <c r="N15">
@@ -1887,126 +2420,129 @@
         <v>187738</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="14.25" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="17" spans="1:17" ht="22.9" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" ht="14.6"/>
+    <row r="17" ht="14.65" spans="2:19">
       <c r="B17" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="O17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="P17" s="15" t="s">
-        <v>99</v>
+        <v>42</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
+        <v>52</v>
+      </c>
+      <c r="S17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" ht="14.65" spans="1:17">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B18">
         <v>29</v>
       </c>
-      <c r="H18" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" s="15" t="s">
-        <v>80</v>
+      <c r="H18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="N18" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="O18" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="P18" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="Q18">
         <v>15.2484</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" ht="14.65" spans="1:17">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B19">
         <v>29</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="L19" s="14" t="s">
+      <c r="H19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" t="s">
+        <v>68</v>
+      </c>
+      <c r="N19" t="s">
+        <v>69</v>
+      </c>
+      <c r="O19" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q19">
+        <v>15.1697</v>
+      </c>
+    </row>
+    <row r="20" ht="14.65" spans="1:17">
+      <c r="A20" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="M19" t="s">
-        <v>74</v>
-      </c>
-      <c r="N19" t="s">
-        <v>75</v>
-      </c>
-      <c r="O19" t="s">
-        <v>76</v>
-      </c>
-      <c r="P19" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q19">
-        <v>15.169700000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="B20" s="11">
         <v>29</v>
       </c>
       <c r="D20">
@@ -2015,20 +2551,20 @@
       <c r="E20">
         <v>334368</v>
       </c>
-      <c r="H20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>43</v>
+      <c r="H20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="M20" t="s">
         <v>77</v>
@@ -2040,17 +2576,17 @@
         <v>79</v>
       </c>
       <c r="P20" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="Q20">
-        <v>15.207100000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="9">
+        <v>15.2071</v>
+      </c>
+    </row>
+    <row r="21" ht="14.65" spans="1:17">
+      <c r="A21" s="12">
         <v>2023</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="12">
         <v>29.8</v>
       </c>
       <c r="D21">
@@ -2059,42 +2595,42 @@
       <c r="E21">
         <v>327036</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>48</v>
+      <c r="H21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="O21" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="P21" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="Q21">
         <v>15.1852</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="8">
+    <row r="22" ht="14.65" spans="1:17">
+      <c r="A22" s="11">
         <v>2022</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="11">
         <v>30.5</v>
       </c>
       <c r="D22">
@@ -2103,42 +2639,42 @@
       <c r="E22">
         <v>320591</v>
       </c>
-      <c r="H22" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>53</v>
+      <c r="H22" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="M22" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="N22" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O22" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q22">
         <v>15.0664</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="9">
+    <row r="23" ht="14.65" spans="1:17">
+      <c r="A23" s="12">
         <v>2021</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="12">
         <v>29.8</v>
       </c>
       <c r="D23">
@@ -2147,42 +2683,42 @@
       <c r="E23">
         <v>312226</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>58</v>
+      <c r="H23" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="M23" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N23" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="O23" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="P23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Q23">
-        <v>14.843299999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="8">
+        <v>14.8433</v>
+      </c>
+    </row>
+    <row r="24" ht="14.65" spans="1:17">
+      <c r="A24" s="11">
         <v>2020</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="11">
         <v>30.2</v>
       </c>
       <c r="D24">
@@ -2191,42 +2727,42 @@
       <c r="E24">
         <v>283832</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>63</v>
+      <c r="H24" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="N24" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="O24" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="P24" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="Q24">
         <v>14.7879</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="9">
+    <row r="25" ht="14.65" spans="1:17">
+      <c r="A25" s="12">
         <v>2019</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="12">
         <v>28.2</v>
       </c>
       <c r="D25">
@@ -2235,42 +2771,42 @@
       <c r="E25">
         <v>270874</v>
       </c>
-      <c r="H25" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>68</v>
+      <c r="H25" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="M25" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="N25" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="O25" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="P25" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="Q25">
         <v>14.8826</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.4">
-      <c r="A26" s="8">
+    <row r="26" ht="15" spans="1:17">
+      <c r="A26" s="11">
         <v>2018</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="11">
         <v>28.4</v>
       </c>
       <c r="D26">
@@ -2279,18 +2815,18 @@
       <c r="E26">
         <v>235714</v>
       </c>
-      <c r="P26" s="16" t="s">
-        <v>125</v>
+      <c r="P26" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="Q26">
-        <v>-8.3949999999999997E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.4">
-      <c r="A27" s="9">
+        <v>-0.008395</v>
+      </c>
+    </row>
+    <row r="27" ht="15" spans="1:17">
+      <c r="A27" s="12">
         <v>2017</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="12">
         <v>29.3</v>
       </c>
       <c r="D27">
@@ -2299,18 +2835,18 @@
       <c r="E27">
         <v>224050</v>
       </c>
-      <c r="P27" s="16" t="s">
-        <v>126</v>
+      <c r="P27" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="Q27">
-        <v>17.375830000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A28" s="8">
+        <v>17.37583</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="11">
         <v>2016</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="11">
         <v>30.1</v>
       </c>
       <c r="D28">
@@ -2320,17 +2856,17 @@
         <v>196018</v>
       </c>
       <c r="P28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q28">
-        <v>-0.38774399999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A29" s="9">
+        <v>-0.387744</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="12">
         <v>2015</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="12">
         <v>30.6</v>
       </c>
       <c r="D29">
@@ -2340,11 +2876,11 @@
         <v>200158</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A30" s="8">
+    <row r="30" spans="1:5">
+      <c r="A30" s="11">
         <v>2014</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="11">
         <v>30.8</v>
       </c>
       <c r="D30">
@@ -2354,11 +2890,11 @@
         <v>214292</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A31" s="9">
+    <row r="31" spans="1:5">
+      <c r="A31" s="12">
         <v>2013</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="12">
         <v>30.9</v>
       </c>
       <c r="D31">
@@ -2368,7 +2904,7 @@
         <v>208854</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="4:5">
       <c r="D32">
         <v>2007</v>
       </c>
@@ -2376,7 +2912,7 @@
         <v>206101</v>
       </c>
     </row>
-    <row r="33" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="4:5">
       <c r="D33">
         <v>2008</v>
       </c>
@@ -2384,7 +2920,7 @@
         <v>181824</v>
       </c>
     </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="4:5">
       <c r="D34">
         <v>2009</v>
       </c>
@@ -2392,7 +2928,7 @@
         <v>183275</v>
       </c>
     </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="4:5">
       <c r="D35">
         <v>2010</v>
       </c>
@@ -2400,7 +2936,7 @@
         <v>215452</v>
       </c>
     </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="4:5">
       <c r="D36">
         <v>2011</v>
       </c>
@@ -2408,7 +2944,7 @@
         <v>179536</v>
       </c>
     </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="4:5">
       <c r="D37">
         <v>2012</v>
       </c>
@@ -2416,7 +2952,7 @@
         <v>157597</v>
       </c>
     </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="4:5">
       <c r="D38">
         <v>2013</v>
       </c>
@@ -2424,7 +2960,7 @@
         <v>147468</v>
       </c>
     </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="4:5">
       <c r="D39">
         <v>2014</v>
       </c>
@@ -2432,7 +2968,7 @@
         <v>182207</v>
       </c>
     </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="4:5">
       <c r="D40">
         <v>2015</v>
       </c>
@@ -2440,7 +2976,7 @@
         <v>161618</v>
       </c>
     </row>
-    <row r="41" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="4:5">
       <c r="D41">
         <v>2016</v>
       </c>
@@ -2448,7 +2984,7 @@
         <v>151683</v>
       </c>
     </row>
-    <row r="42" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="4:5">
       <c r="D42">
         <v>2017</v>
       </c>
@@ -2456,7 +2992,7 @@
         <v>183698</v>
       </c>
     </row>
-    <row r="43" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="4:5">
       <c r="D43">
         <v>2018</v>
       </c>
@@ -2464,7 +3000,7 @@
         <v>179900</v>
       </c>
     </row>
-    <row r="44" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="4:5">
       <c r="D44">
         <v>2019</v>
       </c>
@@ -2472,7 +3008,7 @@
         <v>163200</v>
       </c>
     </row>
-    <row r="45" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="4:5">
       <c r="D45">
         <v>2020</v>
       </c>
@@ -2480,7 +3016,7 @@
         <v>116600</v>
       </c>
     </row>
-    <row r="46" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="4:5">
       <c r="D46">
         <v>2021</v>
       </c>
@@ -2488,7 +3024,7 @@
         <v>112200</v>
       </c>
     </row>
-    <row r="47" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="4:5">
       <c r="D47">
         <v>2022</v>
       </c>
@@ -2497,19 +3033,20 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B67E83-0E83-4899-A591-AD36AC8E80A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2518,8 +3055,6 @@
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38748CD9-CB4B-4D49-BDEE-2154210B67A9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
-  </ds:schemaRefs>
+  <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
--- a/在校学生数统计.xlsx
+++ b/在校学生数统计.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jianmoxiaosai\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CBEB28-8DF1-4482-891D-063B52A4BAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表 3" sheetId="2" r:id="rId1"/>
@@ -31,15 +37,15 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="查询 - 表 3" description="与工作簿中“表 3”查询的连接。" type="5" background="1" refreshedVersion="2" saveData="1">
-    <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=&quot;表 3&quot;;Extended Properties=&quot;&quot;" command="SELECT * FROM [表 3]" commandType="2"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="查询 - 表 3" description="与工作簿中“表 3”查询的连接。" type="5" refreshedVersion="2" background="1" saveData="1">
+    <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=&quot;表 3&quot;;Extended Properties=&quot;&quot;" command="SELECT * FROM [表 3]"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
   <si>
     <t>高等教育</t>
   </si>
@@ -200,9 +206,6 @@
     <t>义务教育生师比</t>
   </si>
   <si>
-    <t>本科就业率</t>
-  </si>
-  <si>
     <t>2016 年</t>
   </si>
   <si>
@@ -426,19 +429,29 @@
   </si>
   <si>
     <t>相关系数r</t>
+  </si>
+  <si>
+    <t>高等教育招生人数(万)</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>预测2024</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>预测2025</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>预测2026</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,7 +470,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -469,7 +482,7 @@
       <sz val="11"/>
       <color rgb="FF4B4B4B"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -494,7 +507,7 @@
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -505,161 +518,44 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,194 +574,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -907,254 +617,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1204,65 +686,32 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{732C7FD2-0383-4880-ACD7-CD91F346A31C}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1540,30 +989,31 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.66371681415929" customWidth="1"/>
-    <col min="8" max="8" width="13.5309734513274" customWidth="1"/>
-    <col min="9" max="9" width="42.3362831858407" customWidth="1"/>
-    <col min="10" max="10" width="39.6017699115044" customWidth="1"/>
-    <col min="11" max="11" width="18.3362831858407" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.53125" customWidth="1"/>
+    <col min="9" max="9" width="42.33203125" customWidth="1"/>
+    <col min="10" max="10" width="39.59765625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="15" width="12.3982300884956" customWidth="1"/>
-    <col min="16" max="16" width="14.2654867256637" customWidth="1"/>
-    <col min="17" max="17" width="11.2035398230088" customWidth="1"/>
-    <col min="21" max="21" width="16.7345132743363" customWidth="1"/>
-    <col min="22" max="22" width="13.5309734513274" customWidth="1"/>
-    <col min="23" max="23" width="12.929203539823" customWidth="1"/>
+    <col min="14" max="15" width="12.3984375" customWidth="1"/>
+    <col min="16" max="16" width="14.265625" customWidth="1"/>
+    <col min="17" max="17" width="11.19921875" customWidth="1"/>
+    <col min="19" max="19" width="19.59765625" customWidth="1"/>
+    <col min="21" max="21" width="16.73046875" customWidth="1"/>
+    <col min="22" max="22" width="13.53125" customWidth="1"/>
+    <col min="23" max="23" width="12.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" spans="2:22">
+    <row r="1" spans="1:22" ht="33.75" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1628,7 +1078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2013</v>
       </c>
@@ -1688,7 +1138,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:20">
+    <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -1748,7 +1198,7 @@
         <v>56.8</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -1808,7 +1258,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:22">
+    <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>2016</v>
       </c>
@@ -1859,7 +1309,7 @@
         <v>186492</v>
       </c>
       <c r="P5" s="2">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="S5" s="2">
         <v>2567</v>
@@ -1874,7 +1324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:22">
+    <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2017</v>
       </c>
@@ -1940,7 +1390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:22">
+    <row r="7" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -2006,7 +1456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:22">
+    <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -2072,7 +1522,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="1:22">
+    <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -2138,7 +1588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="1:22">
+    <row r="10" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>2021</v>
       </c>
@@ -2201,7 +1651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="1:22">
+    <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>2022</v>
       </c>
@@ -2252,7 +1702,7 @@
         <v>193917</v>
       </c>
       <c r="S11" s="16">
-        <v>2347.7</v>
+        <v>2347.6999999999998</v>
       </c>
       <c r="T11" s="16">
         <v>63.7</v>
@@ -2264,7 +1714,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:22">
+    <row r="12" spans="1:22" ht="15" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2023</v>
       </c>
@@ -2326,7 +1776,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -2356,9 +1806,8 @@
       <c r="O13">
         <v>188352</v>
       </c>
-      <c r="U13" s="17"/>
-    </row>
-    <row r="14" spans="1:15">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2370,7 +1819,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="5"/>
       <c r="G14" s="8">
-        <v>570889.7</v>
+        <v>570889.69999999995</v>
       </c>
       <c r="H14">
         <v>1629434</v>
@@ -2389,7 +1838,7 @@
         <v>188045</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2401,7 +1850,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="5"/>
       <c r="G15" s="8">
-        <v>540504.2</v>
+        <v>540504.19999999995</v>
       </c>
       <c r="H15">
         <v>1602655</v>
@@ -2420,8 +1869,7 @@
         <v>187738</v>
       </c>
     </row>
-    <row r="16" ht="14.6"/>
-    <row r="17" ht="14.65" spans="2:19">
+    <row r="17" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>41</v>
       </c>
@@ -2458,11 +1906,11 @@
       <c r="Q17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" ht="14.65" spans="1:17">
+      <c r="S17" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -2470,37 +1918,40 @@
         <v>29</v>
       </c>
       <c r="H18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="J18" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="K18" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="L18" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="M18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="14" t="s">
+      <c r="N18" t="s">
         <v>59</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>60</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>61</v>
-      </c>
-      <c r="P18" t="s">
-        <v>62</v>
       </c>
       <c r="Q18">
         <v>15.2484</v>
       </c>
-    </row>
-    <row r="19" ht="14.65" spans="1:17">
+      <c r="S18" s="19">
+        <v>17.3218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -2508,37 +1959,40 @@
         <v>29</v>
       </c>
       <c r="H19" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="J19" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="K19" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="L19" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="M19" t="s">
         <v>67</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>68</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>69</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>70</v>
       </c>
-      <c r="P19" t="s">
-        <v>71</v>
-      </c>
       <c r="Q19">
-        <v>15.1697</v>
-      </c>
-    </row>
-    <row r="20" ht="14.65" spans="1:17">
+        <v>15.169700000000001</v>
+      </c>
+      <c r="S19" s="19">
+        <v>17.123899999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="10" t="s">
         <v>38</v>
       </c>
@@ -2552,37 +2006,40 @@
         <v>334368</v>
       </c>
       <c r="H20" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="J20" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="K20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="L20" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="M20" t="s">
         <v>76</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>77</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>78</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>79</v>
       </c>
-      <c r="P20" t="s">
-        <v>80</v>
-      </c>
       <c r="Q20">
-        <v>15.2071</v>
-      </c>
-    </row>
-    <row r="21" ht="14.65" spans="1:17">
+        <v>15.207100000000001</v>
+      </c>
+      <c r="S20" s="19">
+        <v>17.554300000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="12">
         <v>2023</v>
       </c>
@@ -2596,37 +2053,40 @@
         <v>327036</v>
       </c>
       <c r="H21" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="J21" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="L21" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="M21" t="s">
         <v>85</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>86</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>87</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>88</v>
-      </c>
-      <c r="P21" t="s">
-        <v>89</v>
       </c>
       <c r="Q21">
         <v>15.1852</v>
       </c>
-    </row>
-    <row r="22" ht="14.65" spans="1:17">
+      <c r="S21" s="19">
+        <v>20.3888</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="11">
         <v>2022</v>
       </c>
@@ -2640,37 +2100,40 @@
         <v>320591</v>
       </c>
       <c r="H22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="K22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="L22" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="L22" s="13" t="s">
+      <c r="M22" t="s">
         <v>94</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>95</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>96</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>97</v>
-      </c>
-      <c r="P22" t="s">
-        <v>98</v>
       </c>
       <c r="Q22">
         <v>15.0664</v>
       </c>
-    </row>
-    <row r="23" ht="14.65" spans="1:17">
+      <c r="S22" s="19">
+        <v>18.906400000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="12">
         <v>2021</v>
       </c>
@@ -2684,37 +2147,40 @@
         <v>312226</v>
       </c>
       <c r="H23" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="J23" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="K23" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="L23" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="M23" t="s">
         <v>103</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>104</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>105</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>106</v>
       </c>
-      <c r="P23" t="s">
-        <v>107</v>
-      </c>
       <c r="Q23">
-        <v>14.8433</v>
-      </c>
-    </row>
-    <row r="24" ht="14.65" spans="1:17">
+        <v>14.843299999999999</v>
+      </c>
+      <c r="S23" s="19">
+        <v>20.630800000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="11">
         <v>2020</v>
       </c>
@@ -2728,37 +2194,40 @@
         <v>283832</v>
       </c>
       <c r="H24" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="J24" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="K24" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="L24" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="M24" t="s">
         <v>112</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>113</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>114</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>115</v>
-      </c>
-      <c r="P24" t="s">
-        <v>116</v>
       </c>
       <c r="Q24">
         <v>14.7879</v>
       </c>
-    </row>
-    <row r="25" ht="14.65" spans="1:17">
+      <c r="S24" s="19">
+        <v>22.270600000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="14.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="12">
         <v>2019</v>
       </c>
@@ -2772,37 +2241,40 @@
         <v>270874</v>
       </c>
       <c r="H25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="J25" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="K25" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="L25" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="L25" s="13" t="s">
+      <c r="M25" t="s">
         <v>121</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>122</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>123</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>124</v>
-      </c>
-      <c r="P25" t="s">
-        <v>125</v>
       </c>
       <c r="Q25">
         <v>14.8826</v>
       </c>
-    </row>
-    <row r="26" ht="15" spans="1:17">
+      <c r="S25" s="19">
+        <v>21.207799999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15" x14ac:dyDescent="0.4">
       <c r="A26" s="11">
         <v>2018</v>
       </c>
@@ -2815,14 +2287,33 @@
       <c r="E26">
         <v>235714</v>
       </c>
+      <c r="H26" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="L26">
+        <f>SUM(M26:O26)</f>
+        <v>516.81988899999999</v>
+      </c>
+      <c r="M26">
+        <v>283.64881100000002</v>
+      </c>
+      <c r="N26">
+        <v>107.48298200000001</v>
+      </c>
+      <c r="O26">
+        <v>125.688096</v>
+      </c>
       <c r="P26" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q26">
-        <v>-0.008395</v>
-      </c>
-    </row>
-    <row r="27" ht="15" spans="1:17">
+        <v>-8.3949999999999997E-3</v>
+      </c>
+      <c r="S26">
+        <v>0.25771227679999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15" x14ac:dyDescent="0.4">
       <c r="A27" s="12">
         <v>2017</v>
       </c>
@@ -2835,14 +2326,33 @@
       <c r="E27">
         <v>224050</v>
       </c>
+      <c r="H27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="L27" s="21">
+        <f>SUM(M27:O27)</f>
+        <v>521.43227100000001</v>
+      </c>
+      <c r="M27">
+        <v>285.08336300000002</v>
+      </c>
+      <c r="N27">
+        <v>109.386723</v>
+      </c>
+      <c r="O27">
+        <v>126.96218500000001</v>
+      </c>
       <c r="P27" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q27">
-        <v>17.37583</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+        <v>17.375830000000001</v>
+      </c>
+      <c r="S27">
+        <v>-11.488249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28" s="11">
         <v>2016</v>
       </c>
@@ -2855,14 +2365,33 @@
       <c r="E28">
         <v>196018</v>
       </c>
+      <c r="H28" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L28">
+        <f>SUM(M28:O28)</f>
+        <v>526.04465100000004</v>
+      </c>
+      <c r="M28">
+        <v>286.51791500000002</v>
+      </c>
+      <c r="N28">
+        <v>111.290463</v>
+      </c>
+      <c r="O28">
+        <v>128.23627300000001</v>
+      </c>
       <c r="P28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q28">
-        <v>-0.387744</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>-0.38774399999999998</v>
+      </c>
+      <c r="S28" s="17">
+        <v>0.67935000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29" s="12">
         <v>2015</v>
       </c>
@@ -2876,7 +2405,7 @@
         <v>200158</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30" s="11">
         <v>2014</v>
       </c>
@@ -2890,7 +2419,7 @@
         <v>214292</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31" s="12">
         <v>2013</v>
       </c>
@@ -2904,7 +2433,7 @@
         <v>208854</v>
       </c>
     </row>
-    <row r="32" spans="4:5">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="D32">
         <v>2007</v>
       </c>
@@ -2912,7 +2441,7 @@
         <v>206101</v>
       </c>
     </row>
-    <row r="33" spans="4:5">
+    <row r="33" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D33">
         <v>2008</v>
       </c>
@@ -2920,7 +2449,7 @@
         <v>181824</v>
       </c>
     </row>
-    <row r="34" spans="4:5">
+    <row r="34" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D34">
         <v>2009</v>
       </c>
@@ -2928,7 +2457,7 @@
         <v>183275</v>
       </c>
     </row>
-    <row r="35" spans="4:5">
+    <row r="35" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D35">
         <v>2010</v>
       </c>
@@ -2936,7 +2465,7 @@
         <v>215452</v>
       </c>
     </row>
-    <row r="36" spans="4:5">
+    <row r="36" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D36">
         <v>2011</v>
       </c>
@@ -2944,7 +2473,7 @@
         <v>179536</v>
       </c>
     </row>
-    <row r="37" spans="4:5">
+    <row r="37" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D37">
         <v>2012</v>
       </c>
@@ -2952,7 +2481,7 @@
         <v>157597</v>
       </c>
     </row>
-    <row r="38" spans="4:5">
+    <row r="38" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D38">
         <v>2013</v>
       </c>
@@ -2960,7 +2489,7 @@
         <v>147468</v>
       </c>
     </row>
-    <row r="39" spans="4:5">
+    <row r="39" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D39">
         <v>2014</v>
       </c>
@@ -2968,7 +2497,7 @@
         <v>182207</v>
       </c>
     </row>
-    <row r="40" spans="4:5">
+    <row r="40" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D40">
         <v>2015</v>
       </c>
@@ -2976,7 +2505,7 @@
         <v>161618</v>
       </c>
     </row>
-    <row r="41" spans="4:5">
+    <row r="41" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D41">
         <v>2016</v>
       </c>
@@ -2984,7 +2513,7 @@
         <v>151683</v>
       </c>
     </row>
-    <row r="42" spans="4:5">
+    <row r="42" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D42">
         <v>2017</v>
       </c>
@@ -2992,7 +2521,7 @@
         <v>183698</v>
       </c>
     </row>
-    <row r="43" spans="4:5">
+    <row r="43" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D43">
         <v>2018</v>
       </c>
@@ -3000,7 +2529,7 @@
         <v>179900</v>
       </c>
     </row>
-    <row r="44" spans="4:5">
+    <row r="44" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D44">
         <v>2019</v>
       </c>
@@ -3008,7 +2537,7 @@
         <v>163200</v>
       </c>
     </row>
-    <row r="45" spans="4:5">
+    <row r="45" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D45">
         <v>2020</v>
       </c>
@@ -3016,7 +2545,7 @@
         <v>116600</v>
       </c>
     </row>
-    <row r="46" spans="4:5">
+    <row r="46" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D46">
         <v>2021</v>
       </c>
@@ -3024,7 +2553,7 @@
         <v>112200</v>
       </c>
     </row>
-    <row r="47" spans="4:5">
+    <row r="47" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D47">
         <v>2022</v>
       </c>
@@ -3033,20 +2562,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
